--- a/file/qs-20.xlsx
+++ b/file/qs-20.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,528 +431,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>000920</t>
+          <t>600303</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>沃顿科技</t>
+          <t>曙光股份</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>002165</t>
+          <t>600735</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>红 宝 丽</t>
+          <t>新华锦</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>603200</t>
+          <t>603316</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>诚邦股份</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>002956</t>
+          <t>600281</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>西麦食品</t>
+          <t>华阳新材</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300005</t>
+          <t>002514</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>探路者</t>
+          <t>宝馨科技</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>603697</t>
+          <t>603900</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>有友食品</t>
+          <t>莱绅通灵</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>000597</t>
+          <t>000565</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>东北制药</t>
+          <t>渝三峡Ａ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>600628</t>
+          <t>603168</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>新世界</t>
+          <t>莎普爱思</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>600279</t>
+          <t>002562</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>重庆港</t>
+          <t>兄弟科技</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>605599</t>
+          <t>603028</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>菜百股份</t>
+          <t>赛福天</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>002033</t>
+          <t>600448</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>丽江股份</t>
+          <t>华纺股份</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>002267</t>
+          <t>000632</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>陕天然气</t>
+          <t>三木集团</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>605179</t>
+          <t>002719</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>一鸣食品</t>
+          <t>麦趣尔</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>002749</t>
+          <t>603335</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>国光股份</t>
+          <t>迪生力</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>000848</t>
+          <t>002790</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>承德露露</t>
+          <t>瑞尔特</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>002588</t>
+          <t>600774</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>史丹利</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>300758</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>七彩化学</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>300859</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>西域旅游</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>000915</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>华特达因</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>603099</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>长白山</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>600305</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>恒顺醋业</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>002612</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>朗姿股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>000560</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>我爱我家</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>000716</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>黑芝麻</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>002697</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>红旗连锁</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>300973</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>立高食品</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>603199</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>九华旅游</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>000888</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>峨眉山Ａ</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>605337</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>李子园</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>000753</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>漳州发展</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>002481</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>双塔食品</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>601116</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>三江购物</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>003000</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>劲仔食品</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>300797</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>钢研纳克</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>605338</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>巴比食品</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>600505</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>西昌电力</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>300917</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>特发服务</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>000601</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>韶能股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>000501</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>武商集团</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>301116</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>益客食品</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>600300</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>维维股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>600101</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>明星电力</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>601579</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>会稽山</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>000965</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>天保基建</t>
+          <t>汉商集团</t>
         </is>
       </c>
     </row>
